--- a/ig/DM-SIDOBA/CodeSystem-tre-r422-qualification-orientation.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-tre-r422-qualification-orientation.xlsx
@@ -215,8 +215,8 @@
     <t>Alternative</t>
   </si>
   <si>
-    <t xml:space="preserve">L'orientation alternative est partiellement adaptée au regard des attentes et des besoins évalués de la personne. Elle prend bien en compte la réalité de l'offre disponible. Elle a ainsi plus de chance d'être mise en œuvre.
-L'orientation alternative est aussi appelée "Orientation par défaut". </t>
+    <t>L'orientation alternative est partiellement adaptée au regard des attentes et des besoins évalués de la personne. Elle prend bien en compte la réalité de l'offre disponible. Elle a ainsi plus de chance d'être mise en œuvre.
+L'orientation alternative est aussi appelée "Orientation par défaut".</t>
   </si>
 </sst>
 </file>
